--- a/data/processed/reports/Abnormal_Order_Report_20260623.xlsx
+++ b/data/processed/reports/Abnormal_Order_Report_20260623.xlsx
@@ -450,7 +450,7 @@
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -560,82 +560,82 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ORD-20260623-9037</t>
+          <t>ORD-20260623-9045</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Summit Office Park</t>
+          <t>Apex Manufacturing Plant</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SMALL_BUSINESS</t>
+          <t>INDUSTRIAL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Copy Paper Case</t>
+          <t>High Visibility Safety Vest Pack</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Office Supplies</t>
+          <t>Safety and PPE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>14.5</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>78</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>+4175%</t>
+          <t>+438%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>288</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>$10,087</t>
+          <t>$5,772</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>75/100</t>
+          <t>60/100</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Confirm whether this order is associated with a new project or contract for Summit Office Park; Monitor follow-up orders from Summit Office Park over the next 7–14 days; Consider transferring Copy Paper Case inventory from lower-demand locations if demand persists; Increase procurement planning for Copy Paper Case if demand continues at this level</t>
+          <t>Confirm whether this order is associated with a new project or contract for Apex Manufacturing Plant; Monitor follow-up orders from Apex Manufacturing Plant over the next 7–14 days; Consider transferring High Visibility Safety Vest Pack inventory from lower-demand locations if demand persists; Increase procurement planning for High Visibility Safety Vest Pack if demand continues at this level; Review Apex Manufacturing Plant's broader ordering pattern — 2 of their order lines are flagged abnormal</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>Inventory pressure: this single order consumes about 86% of current network stock, tightening availability for other customers. | Potential stockout risk: Moderate — limited buffer remaining. | Procurement impact: replenishment volume and timing should be reviewed so the spike does not deplete buffer stock. | Customer concentration risk: a single customer is driving an outsized share of demand for this product. | Revenue opportunity: the order carries $10,087 in revenue that should be secured and serviced reliably.</t>
+          <t>Inventory pressure: this single order consumes about 27% of current network stock, tightening availability for other customers. | Potential stockout risk: Low — current stock can absorb the order. | Procurement impact: replenishment volume and timing should be reviewed so the spike does not deplete buffer stock. | Customer concentration risk: Apex Manufacturing Plant has multiple abnormal order lines, increasing the business's dependence on a single account. | Revenue opportunity: the order carries $5,772 in revenue that should be secured and serviced reliably.</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ORD-20260623-9040</t>
+          <t>ORD-20260623-9044</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -672,57 +672,57 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>32</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>+366%</t>
+          <t>+73%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>342</t>
+          <t>310</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>$1,440</t>
+          <t>$1,024</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>58/100</t>
+          <t>23/100</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Confirm whether this order is associated with a new project or contract for Apex Manufacturing Plant; Monitor follow-up orders from Apex Manufacturing Plant over the next 7–14 days; Consider transferring Safety Glasses Pack inventory from lower-demand locations if demand persists; Increase procurement planning for Safety Glasses Pack if demand continues at this level</t>
+          <t>Confirm whether this order is associated with a new project or contract for Apex Manufacturing Plant; Monitor follow-up orders from Apex Manufacturing Plant over the next 7–14 days; Consider transferring Safety Glasses Pack inventory from lower-demand locations if demand persists; Increase procurement planning for Safety Glasses Pack if demand continues at this level; Review Apex Manufacturing Plant's broader ordering pattern — 2 of their order lines are flagged abnormal</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Inventory pressure: this single order consumes about 13% of current network stock, tightening availability for other customers. | Potential stockout risk: Low — current stock can absorb the order. | Procurement impact: replenishment volume and timing should be reviewed so the spike does not deplete buffer stock. | Customer concentration risk: a single customer is driving an outsized share of demand for this product. | Revenue opportunity: the order carries $1,440 in revenue that should be secured and serviced reliably.</t>
+          <t>Inventory pressure: this single order consumes about 10% of current network stock, tightening availability for other customers. | Potential stockout risk: Low — current stock can absorb the order. | Procurement impact: replenishment volume and timing should be reviewed so the spike does not deplete buffer stock. | Customer concentration risk: Apex Manufacturing Plant has multiple abnormal order lines, increasing the business's dependence on a single account. | Revenue opportunity: the order carries $1,024 in revenue that should be secured and serviced reliably.</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>210</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>120%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -794,22 +794,22 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>43/100</t>
+          <t>20/100</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Confirm whether this order is associated with a new project or contract for Lakeside School District; Monitor follow-up orders from Lakeside School District over the next 7–14 days; Consider transferring Pallet Stretch Film Case inventory from lower-demand locations to cover the shortfall; Increase procurement planning for Pallet Stretch Film Case if demand continues at this level</t>
+          <t>Confirm whether this order is associated with a new project or contract for Lakeside School District; Monitor follow-up orders from Lakeside School District over the next 7–14 days; Consider transferring Pallet Stretch Film Case inventory from lower-demand locations if demand persists; Increase procurement planning for Pallet Stretch Film Case if demand continues at this level</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>Inventory pressure: this single order consumes about 120% of current network stock, tightening availability for other customers. | Potential stockout risk: High — order exceeds on-hand stock. | Procurement impact: replenishment volume and timing should be reviewed so the spike does not deplete buffer stock. | Customer concentration risk: a single customer is driving an outsized share of demand for this product. | Revenue opportunity: the order carries $10,560 in revenue that should be secured and serviced reliably.</t>
+          <t>Inventory pressure: this single order consumes about 57% of current network stock, tightening availability for other customers. | Potential stockout risk: Moderate — limited buffer remaining. | Procurement impact: replenishment volume and timing should be reviewed so the spike does not deplete buffer stock. | Customer concentration risk: a single customer is driving an outsized share of demand for this product. | Revenue opportunity: the order carries $10,560 in revenue that should be secured and serviced reliably.</t>
         </is>
       </c>
     </row>
